--- a/MAESTRIA/TIPOLOGIA ESTRUCTURAL/TRABAJO FINAL/formato prime/MEMORIA CALCULO HOSPITAL.xlsx
+++ b/MAESTRIA/TIPOLOGIA ESTRUCTURAL/TRABAJO FINAL/formato prime/MEMORIA CALCULO HOSPITAL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\EXAMEN FINAL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivan\Documents\gitdocs-2026\MAESTRIA\TIPOLOGIA ESTRUCTURAL\TRABAJO FINAL\formato prime\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{536A4932-0908-452E-9C7E-3102FC99E606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B17383-1D13-4118-962B-00F9B38B90F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="2" xr2:uid="{A6F4C03D-0FB8-4EB4-81C4-6D3248E700FE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{A6F4C03D-0FB8-4EB4-81C4-6D3248E700FE}"/>
   </bookViews>
   <sheets>
     <sheet name="PREDIMENCIONAMIENTO" sheetId="1" r:id="rId1"/>
@@ -1478,7 +1478,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1487,17 +1490,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1505,16 +1505,25 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1524,16 +1533,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1541,10 +1541,10 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2564,6 +2564,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2571,7 +2572,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3118,6 +3118,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3125,7 +3126,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3672,6 +3672,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3679,7 +3680,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4139,6 +4139,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4146,7 +4147,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -8248,10 +8248,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="93" t="s">
+      <c r="B2" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="93"/>
+      <c r="C2" s="87"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -8348,13 +8348,13 @@
         <f>15100*SQRT(C13)</f>
         <v>253254.48473140257</v>
       </c>
-      <c r="F13" s="99" t="s">
+      <c r="F13" s="93" t="s">
         <v>17</v>
       </c>
-      <c r="G13" s="99"/>
-      <c r="H13" s="99"/>
-      <c r="I13" s="99"/>
-      <c r="J13" s="99"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="93"/>
+      <c r="J13" s="93"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -8373,13 +8373,13 @@
       <c r="E14" s="8">
         <v>2039321.85</v>
       </c>
-      <c r="F14" s="99" t="s">
+      <c r="F14" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="G14" s="99"/>
-      <c r="H14" s="99"/>
-      <c r="I14" s="99"/>
-      <c r="J14" s="99"/>
+      <c r="G14" s="93"/>
+      <c r="H14" s="93"/>
+      <c r="I14" s="93"/>
+      <c r="J14" s="93"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
@@ -8393,23 +8393,23 @@
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="99" t="s">
+      <c r="F15" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="G15" s="99"/>
-      <c r="H15" s="99"/>
-      <c r="I15" s="99"/>
-      <c r="J15" s="99"/>
+      <c r="G15" s="93"/>
+      <c r="H15" s="93"/>
+      <c r="I15" s="93"/>
+      <c r="J15" s="93"/>
     </row>
     <row r="17" spans="1:6" ht="30" x14ac:dyDescent="0.4">
-      <c r="A17" s="92" t="s">
+      <c r="A17" s="97" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="92"/>
-      <c r="C17" s="92"/>
-      <c r="D17" s="92"/>
-      <c r="E17" s="92"/>
-      <c r="F17" s="92"/>
+      <c r="B17" s="97"/>
+      <c r="C17" s="97"/>
+      <c r="D17" s="97"/>
+      <c r="E17" s="97"/>
+      <c r="F17" s="97"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
@@ -8421,10 +8421,10 @@
       <c r="E18" s="10"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="97" t="s">
+      <c r="A19" s="96" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="97"/>
+      <c r="B19" s="96"/>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
@@ -8523,12 +8523,12 @@
       <c r="E27" s="10"/>
     </row>
     <row r="28" spans="1:6" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A28" s="96" t="str">
+      <c r="A28" s="92" t="str">
         <f>CONCATENATE("VX ",B23*100,"cmX",B26*100,"cm")</f>
         <v>VX 50cmX30cm</v>
       </c>
-      <c r="B28" s="96"/>
-      <c r="C28" s="96"/>
+      <c r="B28" s="92"/>
+      <c r="C28" s="92"/>
       <c r="D28" s="10"/>
       <c r="E28" s="30"/>
     </row>
@@ -8569,10 +8569,10 @@
       <c r="E31" s="10"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="97" t="s">
+      <c r="A34" s="96" t="s">
         <v>35</v>
       </c>
-      <c r="B34" s="97"/>
+      <c r="B34" s="96"/>
       <c r="C34" s="10"/>
       <c r="D34" s="10"/>
       <c r="E34" s="10"/>
@@ -8671,12 +8671,12 @@
       <c r="E42" s="10"/>
     </row>
     <row r="43" spans="1:5" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A43" s="96" t="str">
+      <c r="A43" s="92" t="str">
         <f>CONCATENATE("VY ",B38*100,"cmX",B41*100,"cm")</f>
         <v>VY 45cmX25cm</v>
       </c>
-      <c r="B43" s="96"/>
-      <c r="C43" s="96"/>
+      <c r="B43" s="92"/>
+      <c r="C43" s="92"/>
       <c r="D43" s="10"/>
       <c r="E43" s="31"/>
     </row>
@@ -8717,10 +8717,10 @@
       <c r="E46" s="10"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="98" t="s">
+      <c r="A49" s="91" t="s">
         <v>36</v>
       </c>
-      <c r="B49" s="98"/>
+      <c r="B49" s="91"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
@@ -8945,12 +8945,12 @@
       </c>
     </row>
     <row r="69" spans="1:5" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A69" s="96" t="str">
+      <c r="A69" s="92" t="str">
         <f>CONCATENATE("C ",A67,"cmX",B67,"cm")</f>
         <v>C 45cmX45cm</v>
       </c>
-      <c r="B69" s="96"/>
-      <c r="C69" s="96"/>
+      <c r="B69" s="92"/>
+      <c r="C69" s="92"/>
       <c r="E69" s="32"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -8992,10 +8992,10 @@
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78" s="98" t="s">
+      <c r="A78" s="91" t="s">
         <v>50</v>
       </c>
-      <c r="B78" s="98"/>
+      <c r="B78" s="91"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="11" t="s">
@@ -9079,42 +9079,42 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A90" s="96" t="str">
+      <c r="A90" s="92" t="str">
         <f>CONCATENATE("Losa ",B87," cm")</f>
         <v>Losa 14 cm</v>
       </c>
-      <c r="B90" s="96"/>
-      <c r="C90" s="96"/>
+      <c r="B90" s="92"/>
+      <c r="C90" s="92"/>
       <c r="E90" s="16"/>
     </row>
     <row r="93" spans="1:6" ht="30" x14ac:dyDescent="0.4">
-      <c r="A93" s="92" t="s">
+      <c r="A93" s="97" t="s">
         <v>59</v>
       </c>
-      <c r="B93" s="92"/>
-      <c r="C93" s="92"/>
-      <c r="D93" s="92"/>
-      <c r="E93" s="92"/>
-      <c r="F93" s="92"/>
+      <c r="B93" s="97"/>
+      <c r="C93" s="97"/>
+      <c r="D93" s="97"/>
+      <c r="E93" s="97"/>
+      <c r="F93" s="97"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C95" s="91" t="s">
+      <c r="C95" s="98" t="s">
         <v>70</v>
       </c>
-      <c r="D95" s="91"/>
-      <c r="E95" s="91"/>
+      <c r="D95" s="98"/>
+      <c r="E95" s="98"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C96" s="93"/>
-      <c r="D96" s="93"/>
-      <c r="E96" s="93"/>
+      <c r="C96" s="87"/>
+      <c r="D96" s="87"/>
+      <c r="E96" s="87"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="87" t="s">
+      <c r="A97" s="99" t="s">
         <v>60</v>
       </c>
-      <c r="B97" s="87"/>
-      <c r="C97" s="87"/>
+      <c r="B97" s="99"/>
+      <c r="C97" s="99"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B99" s="19" t="s">
@@ -9162,11 +9162,11 @@
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" s="87" t="s">
+      <c r="A106" s="99" t="s">
         <v>67</v>
       </c>
-      <c r="B106" s="87"/>
-      <c r="C106" s="87"/>
+      <c r="B106" s="99"/>
+      <c r="C106" s="99"/>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B108" s="19" t="s">
@@ -9206,18 +9206,18 @@
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C114" s="91" t="s">
+      <c r="C114" s="98" t="s">
         <v>71</v>
       </c>
-      <c r="D114" s="91"/>
-      <c r="E114" s="91"/>
+      <c r="D114" s="98"/>
+      <c r="E114" s="98"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="87" t="s">
+      <c r="A116" s="99" t="s">
         <v>72</v>
       </c>
-      <c r="B116" s="87"/>
-      <c r="C116" s="87"/>
+      <c r="B116" s="99"/>
+      <c r="C116" s="99"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B118" s="11" t="s">
@@ -9226,11 +9226,11 @@
       <c r="C118" s="33">
         <v>163</v>
       </c>
-      <c r="D118" s="88" t="s">
+      <c r="D118" s="89" t="s">
         <v>76</v>
       </c>
-      <c r="E118" s="89"/>
-      <c r="F118" s="89"/>
+      <c r="E118" s="90"/>
+      <c r="F118" s="90"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B119" s="11" t="s">
@@ -9240,11 +9240,11 @@
         <f>0.01*2000</f>
         <v>20</v>
       </c>
-      <c r="D119" s="88" t="s">
+      <c r="D119" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="E119" s="89"/>
-      <c r="F119" s="89"/>
+      <c r="E119" s="90"/>
+      <c r="F119" s="90"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B120" s="19"/>
@@ -9269,11 +9269,11 @@
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="87" t="s">
+      <c r="A125" s="99" t="s">
         <v>78</v>
       </c>
-      <c r="B125" s="87"/>
-      <c r="C125" s="87"/>
+      <c r="B125" s="99"/>
+      <c r="C125" s="99"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B127" s="11" t="s">
@@ -9282,11 +9282,11 @@
       <c r="C127" s="33">
         <v>163</v>
       </c>
-      <c r="D127" s="88" t="s">
+      <c r="D127" s="89" t="s">
         <v>76</v>
       </c>
-      <c r="E127" s="89"/>
-      <c r="F127" s="89"/>
+      <c r="E127" s="90"/>
+      <c r="F127" s="90"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B128" s="11" t="s">
@@ -9296,11 +9296,11 @@
         <f>0.01*2000</f>
         <v>20</v>
       </c>
-      <c r="D128" s="88" t="s">
+      <c r="D128" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="E128" s="89"/>
-      <c r="F128" s="89"/>
+      <c r="E128" s="90"/>
+      <c r="F128" s="90"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B129" s="19"/>
@@ -9346,21 +9346,21 @@
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="90" t="s">
+      <c r="A137" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="B137" s="90"/>
+      <c r="B137" s="88"/>
       <c r="C137" s="36">
         <f>C131+C135</f>
         <v>240</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="87" t="s">
+      <c r="A140" s="99" t="s">
         <v>98</v>
       </c>
-      <c r="B140" s="87"/>
-      <c r="C140" s="87"/>
+      <c r="B140" s="99"/>
+      <c r="C140" s="99"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B141" s="39" t="s">
@@ -9369,11 +9369,11 @@
       <c r="C141" s="40">
         <v>163</v>
       </c>
-      <c r="D141" s="88" t="s">
+      <c r="D141" s="89" t="s">
         <v>76</v>
       </c>
-      <c r="E141" s="89"/>
-      <c r="F141" s="89"/>
+      <c r="E141" s="90"/>
+      <c r="F141" s="90"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B142" s="11" t="s">
@@ -9383,11 +9383,11 @@
         <f>0.01*2000</f>
         <v>20</v>
       </c>
-      <c r="D142" s="88" t="s">
+      <c r="D142" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="E142" s="89"/>
-      <c r="F142" s="89"/>
+      <c r="E142" s="90"/>
+      <c r="F142" s="90"/>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B143" s="19"/>
@@ -9412,11 +9412,11 @@
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C148" s="91" t="s">
+      <c r="C148" s="98" t="s">
         <v>82</v>
       </c>
-      <c r="D148" s="91"/>
-      <c r="E148" s="91"/>
+      <c r="D148" s="98"/>
+      <c r="E148" s="98"/>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B150" s="19" t="s">
@@ -9467,81 +9467,66 @@
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B157" s="93" t="s">
+      <c r="B157" s="87" t="s">
         <v>90</v>
       </c>
-      <c r="C157" s="93"/>
-      <c r="D157" s="89" t="s">
+      <c r="C157" s="87"/>
+      <c r="D157" s="90" t="s">
         <v>97</v>
       </c>
-      <c r="E157" s="89"/>
-      <c r="F157" s="89"/>
+      <c r="E157" s="90"/>
+      <c r="F157" s="90"/>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A158" s="90" t="s">
+      <c r="A158" s="88" t="s">
         <v>91</v>
       </c>
-      <c r="B158" s="90"/>
+      <c r="B158" s="88"/>
       <c r="C158" s="33">
         <v>200</v>
       </c>
-      <c r="D158" s="88" t="s">
+      <c r="D158" s="89" t="s">
         <v>94</v>
       </c>
-      <c r="E158" s="89"/>
+      <c r="E158" s="90"/>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A159" s="90" t="s">
+      <c r="A159" s="88" t="s">
         <v>92</v>
       </c>
-      <c r="B159" s="90"/>
+      <c r="B159" s="88"/>
       <c r="C159" s="33">
         <v>85</v>
       </c>
-      <c r="D159" s="88" t="s">
+      <c r="D159" s="89" t="s">
         <v>95</v>
       </c>
-      <c r="E159" s="89"/>
+      <c r="E159" s="90"/>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A160" s="90" t="s">
+      <c r="A160" s="88" t="s">
         <v>93</v>
       </c>
-      <c r="B160" s="90"/>
+      <c r="B160" s="88"/>
       <c r="C160" s="33">
         <f>10*14</f>
         <v>140</v>
       </c>
-      <c r="D160" s="88" t="s">
+      <c r="D160" s="89" t="s">
         <v>96</v>
       </c>
-      <c r="E160" s="89"/>
+      <c r="E160" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="B157:C157"/>
-    <mergeCell ref="A158:B158"/>
-    <mergeCell ref="A159:B159"/>
-    <mergeCell ref="A160:B160"/>
-    <mergeCell ref="D158:E158"/>
-    <mergeCell ref="D159:E159"/>
-    <mergeCell ref="D160:E160"/>
-    <mergeCell ref="D157:F157"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A90:C90"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F14:J14"/>
-    <mergeCell ref="F15:J15"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A125:C125"/>
+    <mergeCell ref="D127:F127"/>
+    <mergeCell ref="D128:F128"/>
+    <mergeCell ref="A137:B137"/>
+    <mergeCell ref="C148:E148"/>
+    <mergeCell ref="D141:F141"/>
+    <mergeCell ref="D142:F142"/>
+    <mergeCell ref="A140:C140"/>
     <mergeCell ref="C114:E114"/>
     <mergeCell ref="A116:C116"/>
     <mergeCell ref="D118:F118"/>
@@ -9551,14 +9536,29 @@
     <mergeCell ref="A106:C106"/>
     <mergeCell ref="C96:E96"/>
     <mergeCell ref="C95:E95"/>
-    <mergeCell ref="A125:C125"/>
-    <mergeCell ref="D127:F127"/>
-    <mergeCell ref="D128:F128"/>
-    <mergeCell ref="A137:B137"/>
-    <mergeCell ref="C148:E148"/>
-    <mergeCell ref="D141:F141"/>
-    <mergeCell ref="D142:F142"/>
-    <mergeCell ref="A140:C140"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A90:C90"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="F15:J15"/>
+    <mergeCell ref="B157:C157"/>
+    <mergeCell ref="A158:B158"/>
+    <mergeCell ref="A159:B159"/>
+    <mergeCell ref="A160:B160"/>
+    <mergeCell ref="D158:E158"/>
+    <mergeCell ref="D159:E159"/>
+    <mergeCell ref="D160:E160"/>
+    <mergeCell ref="D157:F157"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B26 B41" xr:uid="{328BDB17-1174-4B69-8810-57AED7F9974B}">
@@ -9586,20 +9586,20 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="90" t="s">
+      <c r="A4" s="88" t="s">
         <v>100</v>
       </c>
-      <c r="B4" s="90"/>
+      <c r="B4" s="88"/>
       <c r="C4" s="20">
         <f>18*10</f>
         <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="88" t="s">
         <v>101</v>
       </c>
-      <c r="B5" s="90"/>
+      <c r="B5" s="88"/>
       <c r="C5" s="18">
         <v>3</v>
       </c>
@@ -9608,20 +9608,20 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="90" t="s">
+      <c r="A6" s="88" t="s">
         <v>102</v>
       </c>
-      <c r="B6" s="90"/>
+      <c r="B6" s="88"/>
       <c r="C6" s="21">
         <f>C4*C5</f>
         <v>540</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="90" t="s">
+      <c r="A7" s="88" t="s">
         <v>103</v>
       </c>
-      <c r="B7" s="90"/>
+      <c r="B7" s="88"/>
       <c r="C7" s="18">
         <v>11</v>
       </c>
@@ -9637,37 +9637,37 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="105" t="s">
+      <c r="A9" s="109" t="s">
         <v>113</v>
       </c>
-      <c r="B9" s="105"/>
+      <c r="B9" s="109"/>
       <c r="C9" s="16" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="89" t="s">
+      <c r="A10" s="90" t="s">
         <v>106</v>
       </c>
-      <c r="B10" s="89"/>
+      <c r="B10" s="90"/>
       <c r="C10" s="44" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="87" t="s">
+      <c r="A12" s="99" t="s">
         <v>108</v>
       </c>
-      <c r="B12" s="87"/>
+      <c r="B12" s="99"/>
       <c r="L12" s="42" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="90" t="s">
+      <c r="A14" s="88" t="s">
         <v>109</v>
       </c>
-      <c r="B14" s="90"/>
+      <c r="B14" s="88"/>
       <c r="C14" s="46">
         <v>0.16</v>
       </c>
@@ -9684,10 +9684,10 @@
       <c r="C15" s="19"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="87" t="s">
+      <c r="A17" s="99" t="s">
         <v>112</v>
       </c>
-      <c r="B17" s="87"/>
+      <c r="B17" s="99"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="106" t="s">
@@ -9696,11 +9696,11 @@
       <c r="B18" s="106"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="93" t="s">
+      <c r="A22" s="87" t="s">
         <v>114</v>
       </c>
-      <c r="B22" s="93"/>
-      <c r="C22" s="93"/>
+      <c r="B22" s="87"/>
+      <c r="C22" s="87"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B24" s="11" t="s">
@@ -9709,10 +9709,10 @@
       <c r="C24" s="18">
         <v>1.46</v>
       </c>
-      <c r="E24" s="89" t="s">
+      <c r="E24" s="90" t="s">
         <v>119</v>
       </c>
-      <c r="F24" s="89"/>
+      <c r="F24" s="90"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B25" s="11" t="s">
@@ -9739,10 +9739,10 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="93" t="s">
+      <c r="A29" s="87" t="s">
         <v>120</v>
       </c>
-      <c r="B29" s="93"/>
+      <c r="B29" s="87"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B30" s="11" t="s">
@@ -9761,12 +9761,12 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="93" t="s">
+      <c r="A33" s="87" t="s">
         <v>123</v>
       </c>
-      <c r="B33" s="93"/>
-      <c r="C33" s="93"/>
-      <c r="D33" s="93"/>
+      <c r="B33" s="87"/>
+      <c r="C33" s="87"/>
+      <c r="D33" s="87"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B34" s="11" t="s">
@@ -9803,11 +9803,11 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="93" t="s">
+      <c r="A40" s="87" t="s">
         <v>128</v>
       </c>
-      <c r="B40" s="93"/>
-      <c r="C40" s="93"/>
+      <c r="B40" s="87"/>
+      <c r="C40" s="87"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B41" s="19" t="s">
@@ -9828,16 +9828,16 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="93" t="s">
+      <c r="A44" s="87" t="s">
         <v>131</v>
       </c>
-      <c r="B44" s="93"/>
+      <c r="B44" s="87"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="90" t="s">
+      <c r="A54" s="88" t="s">
         <v>132</v>
       </c>
-      <c r="B54" s="90"/>
+      <c r="B54" s="88"/>
       <c r="C54" s="106" t="s">
         <v>133</v>
       </c>
@@ -9854,24 +9854,24 @@
       <c r="K55" s="73" t="s">
         <v>281</v>
       </c>
-      <c r="L55" s="87" t="s">
+      <c r="L55" s="99" t="s">
         <v>282</v>
       </c>
-      <c r="M55" s="87"/>
+      <c r="M55" s="99"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="93" t="s">
+      <c r="A57" s="87" t="s">
         <v>135</v>
       </c>
-      <c r="B57" s="93"/>
-      <c r="C57" s="93"/>
+      <c r="B57" s="87"/>
+      <c r="C57" s="87"/>
       <c r="K57" s="73" t="s">
         <v>281</v>
       </c>
-      <c r="L57" s="90" t="s">
+      <c r="L57" s="88" t="s">
         <v>283</v>
       </c>
-      <c r="M57" s="90"/>
+      <c r="M57" s="88"/>
       <c r="N57" t="s">
         <v>280</v>
       </c>
@@ -9887,10 +9887,10 @@
       <c r="K58" s="73" t="s">
         <v>281</v>
       </c>
-      <c r="L58" s="87" t="s">
+      <c r="L58" s="99" t="s">
         <v>284</v>
       </c>
-      <c r="M58" s="87"/>
+      <c r="M58" s="99"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B59" s="49" t="s">
@@ -9926,12 +9926,12 @@
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="93" t="s">
+      <c r="A64" s="87" t="s">
         <v>183</v>
       </c>
-      <c r="B64" s="93"/>
-      <c r="C64" s="93"/>
-      <c r="D64" s="93"/>
+      <c r="B64" s="87"/>
+      <c r="C64" s="87"/>
+      <c r="D64" s="87"/>
     </row>
     <row r="66" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C66" s="47" t="s">
@@ -10951,10 +10951,10 @@
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A170" s="87" t="s">
+      <c r="A170" s="99" t="s">
         <v>144</v>
       </c>
-      <c r="B170" s="87"/>
+      <c r="B170" s="99"/>
       <c r="D170" s="42" t="s">
         <v>149</v>
       </c>
@@ -10991,10 +10991,10 @@
         <f>C174*(C176)^C175</f>
         <v>0.30423136847641769</v>
       </c>
-      <c r="D177" s="104" t="s">
+      <c r="D177" s="108" t="s">
         <v>153</v>
       </c>
-      <c r="E177" s="93"/>
+      <c r="E177" s="87"/>
       <c r="F177" s="62" t="s">
         <v>182</v>
       </c>
@@ -11004,10 +11004,10 @@
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A179" s="87" t="s">
+      <c r="A179" s="99" t="s">
         <v>150</v>
       </c>
-      <c r="B179" s="87"/>
+      <c r="B179" s="99"/>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C181" s="52">
@@ -11036,10 +11036,10 @@
         <f>D182</f>
         <v>0.96360000000000001</v>
       </c>
-      <c r="C184" s="104" t="s">
+      <c r="C184" s="108" t="s">
         <v>152</v>
       </c>
-      <c r="D184" s="93"/>
+      <c r="D184" s="87"/>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" s="11" t="s">
@@ -11084,32 +11084,32 @@
       </c>
     </row>
     <row r="194" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A194" s="87" t="s">
+      <c r="A194" s="99" t="s">
         <v>159</v>
       </c>
-      <c r="B194" s="87"/>
+      <c r="B194" s="99"/>
     </row>
     <row r="195" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C195" s="97" t="s">
+      <c r="C195" s="96" t="s">
         <v>172</v>
       </c>
-      <c r="D195" s="97"/>
-      <c r="E195" s="97"/>
+      <c r="D195" s="96"/>
+      <c r="E195" s="96"/>
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>160</v>
       </c>
-      <c r="B196" s="103" t="s">
+      <c r="B196" s="105" t="s">
         <v>161</v>
       </c>
-      <c r="C196" s="103" t="s">
+      <c r="C196" s="105" t="s">
         <v>162</v>
       </c>
       <c r="D196" s="59" t="s">
         <v>163</v>
       </c>
-      <c r="E196" s="100" t="s">
+      <c r="E196" s="103" t="s">
         <v>171</v>
       </c>
       <c r="F196" s="102" t="s">
@@ -11118,7 +11118,7 @@
       <c r="G196" s="102" t="s">
         <v>174</v>
       </c>
-      <c r="H196" s="100" t="s">
+      <c r="H196" s="103" t="s">
         <v>175</v>
       </c>
       <c r="I196" s="102" t="s">
@@ -11126,15 +11126,15 @@
       </c>
     </row>
     <row r="197" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B197" s="103"/>
-      <c r="C197" s="103"/>
+      <c r="B197" s="105"/>
+      <c r="C197" s="105"/>
       <c r="D197" s="59" t="s">
         <v>164</v>
       </c>
-      <c r="E197" s="101"/>
+      <c r="E197" s="104"/>
       <c r="F197" s="102"/>
       <c r="G197" s="102"/>
-      <c r="H197" s="101"/>
+      <c r="H197" s="104"/>
       <c r="I197" s="102"/>
     </row>
     <row r="198" spans="1:13" x14ac:dyDescent="0.3">
@@ -11279,16 +11279,16 @@
       <c r="A210" t="s">
         <v>160</v>
       </c>
-      <c r="B210" s="103" t="s">
+      <c r="B210" s="105" t="s">
         <v>161</v>
       </c>
-      <c r="C210" s="103" t="s">
+      <c r="C210" s="105" t="s">
         <v>162</v>
       </c>
       <c r="D210" s="59" t="s">
         <v>163</v>
       </c>
-      <c r="E210" s="100" t="s">
+      <c r="E210" s="103" t="s">
         <v>171</v>
       </c>
       <c r="F210" s="102" t="s">
@@ -11297,7 +11297,7 @@
       <c r="G210" s="102" t="s">
         <v>174</v>
       </c>
-      <c r="H210" s="100" t="s">
+      <c r="H210" s="103" t="s">
         <v>175</v>
       </c>
       <c r="I210" s="102" t="s">
@@ -11305,15 +11305,15 @@
       </c>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B211" s="103"/>
-      <c r="C211" s="103"/>
+      <c r="B211" s="105"/>
+      <c r="C211" s="105"/>
       <c r="D211" s="59" t="s">
         <v>164</v>
       </c>
-      <c r="E211" s="101"/>
+      <c r="E211" s="104"/>
       <c r="F211" s="102"/>
       <c r="G211" s="102"/>
-      <c r="H211" s="101"/>
+      <c r="H211" s="104"/>
       <c r="I211" s="102"/>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.3">
@@ -11456,76 +11456,76 @@
       </c>
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A224" s="87" t="s">
+      <c r="A224" s="99" t="s">
         <v>184</v>
       </c>
-      <c r="B224" s="87"/>
+      <c r="B224" s="99"/>
     </row>
     <row r="226" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C226" s="108" t="s">
+      <c r="C226" s="101" t="s">
         <v>185</v>
       </c>
-      <c r="D226" s="108" t="s">
+      <c r="D226" s="101" t="s">
         <v>186</v>
       </c>
       <c r="E226" s="64" t="s">
         <v>187</v>
       </c>
-      <c r="F226" s="108" t="s">
+      <c r="F226" s="101" t="s">
         <v>189</v>
       </c>
-      <c r="G226" s="108" t="s">
+      <c r="G226" s="101" t="s">
         <v>190</v>
       </c>
-      <c r="H226" s="108" t="s">
+      <c r="H226" s="101" t="s">
         <v>191</v>
       </c>
-      <c r="I226" s="108" t="s">
+      <c r="I226" s="101" t="s">
         <v>192</v>
       </c>
-      <c r="J226" s="108" t="s">
+      <c r="J226" s="101" t="s">
         <v>193</v>
       </c>
-      <c r="K226" s="108" t="s">
+      <c r="K226" s="101" t="s">
         <v>194</v>
       </c>
-      <c r="L226" s="108" t="s">
+      <c r="L226" s="101" t="s">
         <v>195</v>
       </c>
-      <c r="M226" s="108" t="s">
+      <c r="M226" s="101" t="s">
         <v>196</v>
       </c>
-      <c r="N226" s="108" t="s">
+      <c r="N226" s="101" t="s">
         <v>197</v>
       </c>
-      <c r="O226" s="108" t="s">
+      <c r="O226" s="101" t="s">
         <v>198</v>
       </c>
-      <c r="P226" s="108" t="s">
+      <c r="P226" s="101" t="s">
         <v>199</v>
       </c>
-      <c r="Q226" s="108" t="s">
+      <c r="Q226" s="101" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="227" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C227" s="108"/>
-      <c r="D227" s="108"/>
+      <c r="C227" s="101"/>
+      <c r="D227" s="101"/>
       <c r="E227" s="64" t="s">
         <v>188</v>
       </c>
-      <c r="F227" s="108"/>
-      <c r="G227" s="108"/>
-      <c r="H227" s="108"/>
-      <c r="I227" s="108"/>
-      <c r="J227" s="108"/>
-      <c r="K227" s="108"/>
-      <c r="L227" s="108"/>
-      <c r="M227" s="108"/>
-      <c r="N227" s="108"/>
-      <c r="O227" s="108"/>
-      <c r="P227" s="108"/>
-      <c r="Q227" s="108"/>
+      <c r="F227" s="101"/>
+      <c r="G227" s="101"/>
+      <c r="H227" s="101"/>
+      <c r="I227" s="101"/>
+      <c r="J227" s="101"/>
+      <c r="K227" s="101"/>
+      <c r="L227" s="101"/>
+      <c r="M227" s="101"/>
+      <c r="N227" s="101"/>
+      <c r="O227" s="101"/>
+      <c r="P227" s="101"/>
+      <c r="Q227" s="101"/>
     </row>
     <row r="228" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C228" s="58" t="s">
@@ -11951,18 +11951,18 @@
       </c>
     </row>
     <row r="240" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A240" s="87" t="s">
+      <c r="A240" s="99" t="s">
         <v>202</v>
       </c>
-      <c r="B240" s="87"/>
-      <c r="C240" s="87"/>
-      <c r="D240" s="87"/>
+      <c r="B240" s="99"/>
+      <c r="C240" s="99"/>
+      <c r="D240" s="99"/>
     </row>
     <row r="242" spans="1:16" ht="33" x14ac:dyDescent="0.3">
-      <c r="C242" s="108" t="s">
+      <c r="C242" s="101" t="s">
         <v>161</v>
       </c>
-      <c r="D242" s="108" t="s">
+      <c r="D242" s="101" t="s">
         <v>162</v>
       </c>
       <c r="E242" s="64" t="s">
@@ -12003,8 +12003,8 @@
       </c>
     </row>
     <row r="243" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C243" s="108"/>
-      <c r="D243" s="108"/>
+      <c r="C243" s="101"/>
+      <c r="D243" s="101"/>
       <c r="E243" s="64" t="s">
         <v>203</v>
       </c>
@@ -12175,27 +12175,27 @@
       </c>
     </row>
     <row r="249" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A249" s="87" t="s">
+      <c r="A249" s="99" t="s">
         <v>216</v>
       </c>
-      <c r="B249" s="87"/>
-      <c r="C249" s="87"/>
-      <c r="D249" s="87"/>
+      <c r="B249" s="99"/>
+      <c r="C249" s="99"/>
+      <c r="D249" s="99"/>
     </row>
     <row r="251" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C251" s="108" t="s">
+      <c r="C251" s="101" t="s">
         <v>217</v>
       </c>
-      <c r="D251" s="108" t="s">
+      <c r="D251" s="101" t="s">
         <v>218</v>
       </c>
-      <c r="E251" s="108" t="s">
+      <c r="E251" s="101" t="s">
         <v>219</v>
       </c>
-      <c r="F251" s="108" t="s">
+      <c r="F251" s="101" t="s">
         <v>220</v>
       </c>
-      <c r="G251" s="108" t="s">
+      <c r="G251" s="101" t="s">
         <v>221</v>
       </c>
       <c r="H251" s="64" t="s">
@@ -12227,11 +12227,11 @@
       </c>
     </row>
     <row r="252" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C252" s="108"/>
-      <c r="D252" s="108"/>
-      <c r="E252" s="108"/>
-      <c r="F252" s="108"/>
-      <c r="G252" s="108"/>
+      <c r="C252" s="101"/>
+      <c r="D252" s="101"/>
+      <c r="E252" s="101"/>
+      <c r="F252" s="101"/>
+      <c r="G252" s="101"/>
       <c r="H252" s="64" t="s">
         <v>223</v>
       </c>
@@ -12614,10 +12614,10 @@
         <f>D263</f>
         <v>63.003500000000003</v>
       </c>
-      <c r="L263" s="109" t="s">
+      <c r="L263" s="100" t="s">
         <v>246</v>
       </c>
-      <c r="M263" s="109"/>
+      <c r="M263" s="100"/>
       <c r="N263" s="68">
         <f>J263/G263</f>
         <v>1.156889352435025</v>
@@ -12651,37 +12651,37 @@
         <f>D264</f>
         <v>63.003500000000003</v>
       </c>
-      <c r="L264" s="109" t="s">
+      <c r="L264" s="100" t="s">
         <v>247</v>
       </c>
-      <c r="M264" s="109"/>
+      <c r="M264" s="100"/>
       <c r="N264" s="68">
         <f>J264/G264</f>
         <v>1.1689373094784419</v>
       </c>
     </row>
     <row r="271" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A271" s="87" t="s">
+      <c r="A271" s="99" t="s">
         <v>250</v>
       </c>
-      <c r="B271" s="87"/>
-      <c r="C271" s="87"/>
-      <c r="D271" s="87"/>
+      <c r="B271" s="99"/>
+      <c r="C271" s="99"/>
+      <c r="D271" s="99"/>
     </row>
     <row r="272" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="C272" s="108" t="s">
+      <c r="C272" s="101" t="s">
         <v>217</v>
       </c>
-      <c r="D272" s="108" t="s">
+      <c r="D272" s="101" t="s">
         <v>218</v>
       </c>
-      <c r="E272" s="108" t="s">
+      <c r="E272" s="101" t="s">
         <v>219</v>
       </c>
-      <c r="F272" s="108" t="s">
+      <c r="F272" s="101" t="s">
         <v>220</v>
       </c>
-      <c r="G272" s="108" t="s">
+      <c r="G272" s="101" t="s">
         <v>221</v>
       </c>
       <c r="H272" s="64" t="s">
@@ -12713,11 +12713,11 @@
       </c>
     </row>
     <row r="273" spans="3:18" x14ac:dyDescent="0.3">
-      <c r="C273" s="108"/>
-      <c r="D273" s="108"/>
-      <c r="E273" s="108"/>
-      <c r="F273" s="108"/>
-      <c r="G273" s="108"/>
+      <c r="C273" s="101"/>
+      <c r="D273" s="101"/>
+      <c r="E273" s="101"/>
+      <c r="F273" s="101"/>
+      <c r="G273" s="101"/>
       <c r="H273" s="64" t="s">
         <v>223</v>
       </c>
@@ -13100,10 +13100,10 @@
         <f>D284</f>
         <v>63.003500000000003</v>
       </c>
-      <c r="L284" s="109" t="s">
+      <c r="L284" s="100" t="s">
         <v>246</v>
       </c>
-      <c r="M284" s="109"/>
+      <c r="M284" s="100"/>
       <c r="N284" s="68">
         <f>J284/G284</f>
         <v>1.1735052143576907</v>
@@ -13137,45 +13137,45 @@
         <f>D285</f>
         <v>63.003500000000003</v>
       </c>
-      <c r="L285" s="109" t="s">
+      <c r="L285" s="100" t="s">
         <v>247</v>
       </c>
-      <c r="M285" s="109"/>
+      <c r="M285" s="100"/>
       <c r="N285" s="68">
         <f>J285/G285</f>
         <v>1.1799645655724196</v>
       </c>
     </row>
     <row r="302" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C302" s="90" t="s">
+      <c r="C302" s="88" t="s">
         <v>268</v>
       </c>
-      <c r="D302" s="90"/>
-      <c r="E302" s="90"/>
+      <c r="D302" s="88"/>
+      <c r="E302" s="88"/>
     </row>
     <row r="303" spans="2:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B303" s="108" t="s">
+      <c r="B303" s="101" t="s">
         <v>161</v>
       </c>
-      <c r="C303" s="108" t="s">
+      <c r="C303" s="101" t="s">
         <v>251</v>
       </c>
-      <c r="D303" s="108" t="s">
+      <c r="D303" s="101" t="s">
         <v>252</v>
       </c>
-      <c r="E303" s="108" t="s">
+      <c r="E303" s="101" t="s">
         <v>217</v>
       </c>
-      <c r="F303" s="108" t="s">
+      <c r="F303" s="101" t="s">
         <v>218</v>
       </c>
-      <c r="G303" s="108" t="s">
+      <c r="G303" s="101" t="s">
         <v>219</v>
       </c>
-      <c r="H303" s="108" t="s">
+      <c r="H303" s="101" t="s">
         <v>220</v>
       </c>
-      <c r="I303" s="108" t="s">
+      <c r="I303" s="101" t="s">
         <v>221</v>
       </c>
       <c r="J303" s="64" t="s">
@@ -13198,14 +13198,14 @@
       </c>
     </row>
     <row r="304" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B304" s="108"/>
-      <c r="C304" s="108"/>
-      <c r="D304" s="108"/>
-      <c r="E304" s="108"/>
-      <c r="F304" s="108"/>
-      <c r="G304" s="108"/>
-      <c r="H304" s="108"/>
-      <c r="I304" s="108"/>
+      <c r="B304" s="101"/>
+      <c r="C304" s="101"/>
+      <c r="D304" s="101"/>
+      <c r="E304" s="101"/>
+      <c r="F304" s="101"/>
+      <c r="G304" s="101"/>
+      <c r="H304" s="101"/>
+      <c r="I304" s="101"/>
       <c r="J304" s="64" t="s">
         <v>254</v>
       </c>
@@ -13478,22 +13478,22 @@
       <c r="G314" s="70"/>
     </row>
     <row r="315" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="E315" s="87" t="s">
+      <c r="E315" s="99" t="s">
         <v>265</v>
       </c>
-      <c r="F315" s="87"/>
-      <c r="G315" s="87" t="s">
+      <c r="F315" s="99"/>
+      <c r="G315" s="99" t="s">
         <v>271</v>
       </c>
-      <c r="H315" s="87"/>
-      <c r="I315" s="87" t="s">
+      <c r="H315" s="99"/>
+      <c r="I315" s="99" t="s">
         <v>272</v>
       </c>
-      <c r="J315" s="87"/>
-      <c r="K315" s="87" t="s">
+      <c r="J315" s="99"/>
+      <c r="K315" s="99" t="s">
         <v>277</v>
       </c>
-      <c r="L315" s="87"/>
+      <c r="L315" s="99"/>
     </row>
     <row r="316" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C316" s="47" t="s">
@@ -13721,6 +13721,82 @@
     </row>
   </sheetData>
   <mergeCells count="92">
+    <mergeCell ref="H210:H211"/>
+    <mergeCell ref="I210:I211"/>
+    <mergeCell ref="B210:B211"/>
+    <mergeCell ref="C210:C211"/>
+    <mergeCell ref="E210:E211"/>
+    <mergeCell ref="F210:F211"/>
+    <mergeCell ref="G210:G211"/>
+    <mergeCell ref="C184:D184"/>
+    <mergeCell ref="D177:E177"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="A179:B179"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A170:B170"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="F196:F197"/>
+    <mergeCell ref="G196:G197"/>
+    <mergeCell ref="H196:H197"/>
+    <mergeCell ref="I196:I197"/>
+    <mergeCell ref="A194:B194"/>
+    <mergeCell ref="B196:B197"/>
+    <mergeCell ref="C196:C197"/>
+    <mergeCell ref="E196:E197"/>
+    <mergeCell ref="C195:E195"/>
+    <mergeCell ref="A224:B224"/>
+    <mergeCell ref="C226:C227"/>
+    <mergeCell ref="D226:D227"/>
+    <mergeCell ref="F226:F227"/>
+    <mergeCell ref="G226:G227"/>
+    <mergeCell ref="N226:N227"/>
+    <mergeCell ref="O226:O227"/>
+    <mergeCell ref="P226:P227"/>
+    <mergeCell ref="Q226:Q227"/>
+    <mergeCell ref="H226:H227"/>
+    <mergeCell ref="I226:I227"/>
+    <mergeCell ref="J226:J227"/>
+    <mergeCell ref="K226:K227"/>
+    <mergeCell ref="L226:L227"/>
+    <mergeCell ref="A240:D240"/>
+    <mergeCell ref="C242:C243"/>
+    <mergeCell ref="D242:D243"/>
+    <mergeCell ref="A249:D249"/>
+    <mergeCell ref="M226:M227"/>
+    <mergeCell ref="C251:C252"/>
+    <mergeCell ref="D251:D252"/>
+    <mergeCell ref="E251:E252"/>
+    <mergeCell ref="F251:F252"/>
+    <mergeCell ref="G251:G252"/>
+    <mergeCell ref="C272:C273"/>
+    <mergeCell ref="D272:D273"/>
+    <mergeCell ref="E272:E273"/>
+    <mergeCell ref="F272:F273"/>
+    <mergeCell ref="G272:G273"/>
+    <mergeCell ref="G303:G304"/>
+    <mergeCell ref="H303:H304"/>
+    <mergeCell ref="I303:I304"/>
+    <mergeCell ref="L263:M263"/>
+    <mergeCell ref="L264:M264"/>
     <mergeCell ref="L55:M55"/>
     <mergeCell ref="L58:M58"/>
     <mergeCell ref="L57:M57"/>
@@ -13737,82 +13813,6 @@
     <mergeCell ref="D303:D304"/>
     <mergeCell ref="E303:E304"/>
     <mergeCell ref="F303:F304"/>
-    <mergeCell ref="G303:G304"/>
-    <mergeCell ref="H303:H304"/>
-    <mergeCell ref="I303:I304"/>
-    <mergeCell ref="L263:M263"/>
-    <mergeCell ref="L264:M264"/>
-    <mergeCell ref="C272:C273"/>
-    <mergeCell ref="D272:D273"/>
-    <mergeCell ref="E272:E273"/>
-    <mergeCell ref="F272:F273"/>
-    <mergeCell ref="G272:G273"/>
-    <mergeCell ref="C251:C252"/>
-    <mergeCell ref="D251:D252"/>
-    <mergeCell ref="E251:E252"/>
-    <mergeCell ref="F251:F252"/>
-    <mergeCell ref="G251:G252"/>
-    <mergeCell ref="A240:D240"/>
-    <mergeCell ref="C242:C243"/>
-    <mergeCell ref="D242:D243"/>
-    <mergeCell ref="A249:D249"/>
-    <mergeCell ref="M226:M227"/>
-    <mergeCell ref="N226:N227"/>
-    <mergeCell ref="O226:O227"/>
-    <mergeCell ref="P226:P227"/>
-    <mergeCell ref="Q226:Q227"/>
-    <mergeCell ref="H226:H227"/>
-    <mergeCell ref="I226:I227"/>
-    <mergeCell ref="J226:J227"/>
-    <mergeCell ref="K226:K227"/>
-    <mergeCell ref="L226:L227"/>
-    <mergeCell ref="A224:B224"/>
-    <mergeCell ref="C226:C227"/>
-    <mergeCell ref="D226:D227"/>
-    <mergeCell ref="F226:F227"/>
-    <mergeCell ref="G226:G227"/>
-    <mergeCell ref="F196:F197"/>
-    <mergeCell ref="G196:G197"/>
-    <mergeCell ref="H196:H197"/>
-    <mergeCell ref="I196:I197"/>
-    <mergeCell ref="A194:B194"/>
-    <mergeCell ref="B196:B197"/>
-    <mergeCell ref="C196:C197"/>
-    <mergeCell ref="E196:E197"/>
-    <mergeCell ref="C195:E195"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A170:B170"/>
-    <mergeCell ref="A64:D64"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C184:D184"/>
-    <mergeCell ref="D177:E177"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="A179:B179"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="H210:H211"/>
-    <mergeCell ref="I210:I211"/>
-    <mergeCell ref="B210:B211"/>
-    <mergeCell ref="C210:C211"/>
-    <mergeCell ref="E210:E211"/>
-    <mergeCell ref="F210:F211"/>
-    <mergeCell ref="G210:G211"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -13829,10 +13829,10 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="98" t="s">
+      <c r="A4" s="91" t="s">
         <v>285</v>
       </c>
-      <c r="B4" s="98"/>
+      <c r="B4" s="91"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -13851,18 +13851,18 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="93" t="s">
+      <c r="A9" s="87" t="s">
         <v>332</v>
       </c>
-      <c r="B9" s="93"/>
-      <c r="C9" s="89" t="s">
+      <c r="B9" s="87"/>
+      <c r="C9" s="90" t="s">
         <v>294</v>
       </c>
-      <c r="D9" s="89"/>
-      <c r="E9" s="89"/>
-      <c r="F9" s="89"/>
-      <c r="G9" s="89"/>
-      <c r="H9" s="89"/>
+      <c r="D9" s="90"/>
+      <c r="E9" s="90"/>
+      <c r="F9" s="90"/>
+      <c r="G9" s="90"/>
+      <c r="H9" s="90"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
@@ -13889,10 +13889,10 @@
       <c r="F11" t="s">
         <v>289</v>
       </c>
-      <c r="G11" s="89" t="s">
+      <c r="G11" s="90" t="s">
         <v>295</v>
       </c>
-      <c r="H11" s="89"/>
+      <c r="H11" s="90"/>
       <c r="K11" s="11"/>
       <c r="L11" s="11"/>
     </row>
@@ -13975,10 +13975,10 @@
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" s="93" t="s">
+      <c r="A18" s="87" t="s">
         <v>333</v>
       </c>
-      <c r="B18" s="93"/>
+      <c r="B18" s="87"/>
       <c r="K18" s="11">
         <v>10</v>
       </c>
@@ -13987,12 +13987,12 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" s="89" t="s">
+      <c r="A19" s="90" t="s">
         <v>297</v>
       </c>
-      <c r="B19" s="89"/>
-      <c r="C19" s="89"/>
-      <c r="D19" s="89"/>
+      <c r="B19" s="90"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="90"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
@@ -14005,10 +14005,10 @@
       <c r="F21" t="s">
         <v>289</v>
       </c>
-      <c r="G21" s="89" t="s">
+      <c r="G21" s="90" t="s">
         <v>300</v>
       </c>
-      <c r="H21" s="89"/>
+      <c r="H21" s="90"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
@@ -14054,17 +14054,17 @@
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E30" s="89" t="s">
+      <c r="E30" s="90" t="s">
         <v>313</v>
       </c>
-      <c r="F30" s="89"/>
-      <c r="G30" s="89"/>
-      <c r="H30" s="89"/>
-      <c r="I30" s="89"/>
-      <c r="J30" s="89"/>
-      <c r="K30" s="89"/>
-      <c r="L30" s="89"/>
-      <c r="M30" s="89"/>
+      <c r="F30" s="90"/>
+      <c r="G30" s="90"/>
+      <c r="H30" s="90"/>
+      <c r="I30" s="90"/>
+      <c r="J30" s="90"/>
+      <c r="K30" s="90"/>
+      <c r="L30" s="90"/>
+      <c r="M30" s="90"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="19" t="s">
@@ -14096,29 +14096,29 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="90" t="s">
+      <c r="A34" s="88" t="s">
         <v>309</v>
       </c>
-      <c r="B34" s="90"/>
+      <c r="B34" s="88"/>
       <c r="C34" s="82">
         <f>B6*2</f>
         <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="93" t="s">
+      <c r="A37" s="87" t="s">
         <v>314</v>
       </c>
-      <c r="B37" s="93"/>
+      <c r="B37" s="87"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="89" t="s">
+      <c r="A38" s="90" t="s">
         <v>315</v>
       </c>
-      <c r="B38" s="89"/>
-      <c r="C38" s="89"/>
-      <c r="D38" s="89"/>
-      <c r="E38" s="89"/>
+      <c r="B38" s="90"/>
+      <c r="C38" s="90"/>
+      <c r="D38" s="90"/>
+      <c r="E38" s="90"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="19" t="s">
@@ -14127,18 +14127,18 @@
       <c r="B40" s="75">
         <v>11.95</v>
       </c>
-      <c r="E40" s="89" t="s">
+      <c r="E40" s="90" t="s">
         <v>318</v>
       </c>
-      <c r="F40" s="89"/>
-      <c r="G40" s="89"/>
-      <c r="H40" s="89"/>
-      <c r="I40" s="89"/>
-      <c r="J40" s="89"/>
-      <c r="K40" s="89"/>
-      <c r="L40" s="89"/>
-      <c r="M40" s="89"/>
-      <c r="N40" s="89"/>
+      <c r="F40" s="90"/>
+      <c r="G40" s="90"/>
+      <c r="H40" s="90"/>
+      <c r="I40" s="90"/>
+      <c r="J40" s="90"/>
+      <c r="K40" s="90"/>
+      <c r="L40" s="90"/>
+      <c r="M40" s="90"/>
+      <c r="N40" s="90"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="19" t="s">
@@ -14153,28 +14153,28 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="98" t="s">
+      <c r="A45" s="91" t="s">
         <v>319</v>
       </c>
-      <c r="B45" s="98"/>
+      <c r="B45" s="91"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="89" t="s">
+      <c r="A47" s="90" t="s">
         <v>320</v>
       </c>
-      <c r="B47" s="89"/>
-      <c r="C47" s="89"/>
-      <c r="D47" s="89"/>
-      <c r="E47" s="89"/>
-      <c r="F47" s="89"/>
-      <c r="G47" s="89"/>
-      <c r="H47" s="89"/>
+      <c r="B47" s="90"/>
+      <c r="C47" s="90"/>
+      <c r="D47" s="90"/>
+      <c r="E47" s="90"/>
+      <c r="F47" s="90"/>
+      <c r="G47" s="90"/>
+      <c r="H47" s="90"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="93" t="s">
+      <c r="A49" s="87" t="s">
         <v>321</v>
       </c>
-      <c r="B49" s="93"/>
+      <c r="B49" s="87"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="11" t="s">
@@ -14194,23 +14194,23 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="98" t="s">
+      <c r="A54" s="91" t="s">
         <v>322</v>
       </c>
-      <c r="B54" s="98"/>
+      <c r="B54" s="91"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D55" s="89" t="s">
+      <c r="D55" s="90" t="s">
         <v>329</v>
       </c>
-      <c r="E55" s="89"/>
-      <c r="F55" s="89"/>
+      <c r="E55" s="90"/>
+      <c r="F55" s="90"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="93" t="s">
+      <c r="A56" s="87" t="s">
         <v>323</v>
       </c>
-      <c r="B56" s="93"/>
+      <c r="B56" s="87"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="110" t="s">
@@ -14257,10 +14257,10 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="93" t="s">
+      <c r="A64" s="87" t="s">
         <v>330</v>
       </c>
-      <c r="B64" s="93"/>
+      <c r="B64" s="87"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="110" t="s">
@@ -14314,18 +14314,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A65:F65"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="E30:M30"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="A56:B56"/>
@@ -14335,6 +14323,18 @@
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A47:H47"/>
     <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A65:F65"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="E30:M30"/>
+    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
